--- a/artfynd/A 54683-2022 artfynd.xlsx
+++ b/artfynd/A 54683-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124558114</v>
+        <v>124558106</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>56725</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,11 +710,15 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -767,7 +771,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>trummar</t>
+          <t>2 på hygge och 3 på intilliggande myr.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124558106</v>
+        <v>124558114</v>
       </c>
       <c r="B3" t="n">
-        <v>56725</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,20 +810,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -829,15 +833,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -890,7 +890,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2 på hygge och 3 på intilliggande myr.</t>
+          <t>trummar</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 54683-2022 artfynd.xlsx
+++ b/artfynd/A 54683-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124558106</v>
+        <v>124558114</v>
       </c>
       <c r="B2" t="n">
-        <v>56725</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,15 +710,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -771,7 +767,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2 på hygge och 3 på intilliggande myr.</t>
+          <t>trummar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124558114</v>
+        <v>124558106</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>56725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,20 +806,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,11 +829,15 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -890,7 +890,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>trummar</t>
+          <t>2 på hygge och 3 på intilliggande myr.</t>
         </is>
       </c>
       <c r="AD3" t="b">
